--- a/release-notes/2026-05/closed-bugs-sle-2026-05.xlsx
+++ b/release-notes/2026-05/closed-bugs-sle-2026-05.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emerson.sharepoint.com/sites/TM-IoTProgram/Shared Documents/ProjectDocuments/SystemLink 2026/2026 Q3 (v.26.5)(releasing out of Cycle 26.C2)/Common docs/26C2 Release Notes/SLE 2026-05 Release Notes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markblack/repos/install-systemlink-enterprise/release-notes/2026-05/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="371" documentId="8_{0357FC32-4DB0-FA47-B55E-60093BEFF741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1AF5967-D5FA-4040-B048-0B823CBF1A08}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA8D62A-7D06-1444-BE6B-C56CFC8B255A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32130" yWindow="-16200" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="closed bugs" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t xml:space="preserve">System report download fails if the systems had a customer property named "Workspace" </t>
+  </si>
+  <si>
+    <t>Auth Bypass possible in Dashboards - CVE-2026-9051</t>
   </si>
 </sst>
 </file>
@@ -939,14 +942,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="81.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="81.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3838012</v>
       </c>
@@ -968,7 +971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3838017</v>
       </c>
@@ -979,7 +982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3885439</v>
       </c>
@@ -990,7 +993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3823757</v>
       </c>
@@ -1001,7 +1004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3832176</v>
       </c>
@@ -1012,7 +1015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3833960</v>
       </c>
@@ -1023,7 +1026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3834073</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3817813</v>
       </c>
@@ -1045,7 +1048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3760319</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3842962</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3877730</v>
       </c>
@@ -1078,7 +1081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3839954</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3839856</v>
       </c>
@@ -1097,6 +1100,17 @@
         <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>3876241</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1109,6 +1123,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="58dd0d8a-0b6e-4df8-afdb-fbe9bd3e42e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8f35f8fb-94b8-4296-88b5-253c68a5f93d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CC68938C25E75A48B38E3943F7278D4C" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="47491c53f29c61f82c19f477ce8142ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="58dd0d8a-0b6e-4df8-afdb-fbe9bd3e42e9" xmlns:ns3="8f35f8fb-94b8-4296-88b5-253c68a5f93d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1234b2eb10b8f208397560529004cbac" ns2:_="" ns3:_="">
     <xsd:import namespace="58dd0d8a-0b6e-4df8-afdb-fbe9bd3e42e9"/>
@@ -1357,27 +1391,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6B2099-BF96-40FC-B6D0-611F0B5B8DEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8f35f8fb-94b8-4296-88b5-253c68a5f93d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="58dd0d8a-0b6e-4df8-afdb-fbe9bd3e42e9"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="58dd0d8a-0b6e-4df8-afdb-fbe9bd3e42e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8f35f8fb-94b8-4296-88b5-253c68a5f93d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F5BA7BF-C649-45A8-BA98-72C6A48D6AFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF8FE16A-F6E2-4383-A6A5-F239117A00DF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1394,29 +1433,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F5BA7BF-C649-45A8-BA98-72C6A48D6AFB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6B2099-BF96-40FC-B6D0-611F0B5B8DEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="8f35f8fb-94b8-4296-88b5-253c68a5f93d"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="58dd0d8a-0b6e-4df8-afdb-fbe9bd3e42e9"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>